--- a/Firmware/Modules/Ui/Buzzer_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/Buzzer_Board_Validation.xlsx
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>period=60000 duty=2 count=1 gap=0 (standard 1 beep: 1000ms/60s) → dutyWindow≈1200? Actually 60000*2/100≈1200 On=1200? Use exact: period=60000 duty=2 count1 gap0</t>
+          <t>period=60000 duty=2 count=1 gap=0 (standard 1 beep 60s) → dutyWindow=1200ms ON=1200ms tail=58800ms nextCheck=120ms</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>On≈1200ms (1000 nominal + remainder) و tail≈58800ms. PASS: یک پالس/60s. FAIL: دو پالس.</t>
+          <t>dutyWindow=1200ms، ON=1200ms، tail=58800ms، nextCheck=120ms. هر 60s یک پالس 1200ms High سپس 58800ms Low. PASS: یک پالس/60s دقیق. FAIL: دو پالس یا زمان اشتباه.</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>PASS: 1 beep/60s exact.</t>
+          <t>PASS: dutyWindow1200 ON1200 tail58800 nextCheck120. FAIL: otherwise.</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr"/>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c6b084f28f2c507cfd342e5dbd0dbd8e45686772</t>
+          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
@@ -3480,8 +3480,8 @@
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
@@ -3503,8 +3503,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"قبول")</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
@@ -3526,8 +3526,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"رد")</t>
         </is>
       </c>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -3549,8 +3549,8 @@
           <t>COUNTIF('برنامه تست'!K5:K200,"در انتظار")</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -3568,8 +3568,8 @@
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -3587,8 +3587,8 @@
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3675,8 +3675,8 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="A2:F2"/>

--- a/Firmware/Modules/Ui/Buzzer_Board_Validation.xlsx
+++ b/Firmware/Modules/Ui/Buzzer_Board_Validation.xlsx
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>c8c0265e2c3086702f1369b50b467011fd967a94</t>
+          <t>TESTER: fill flashed firmware commit</t>
         </is>
       </c>
       <c r="C6" s="26" t="inlineStr">
